--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{646733E9-4B06-4F54-AF8C-C19A48C2627A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D9C0632-04FB-4FBF-A641-0ACCDAE82BCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D9C0632-04FB-4FBF-A641-0ACCDAE82BCF}" activeTab="-1"/>
   </bookViews>
   <sheets>
-    <sheet name="テスト仕様書" sheetId="1" r:id="rId1"/>
+    <sheet name="テスト仕様書" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,12 +34,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>テスト区分</t>
+    <t>ステージ</t>
+  </si>
+  <si>
+    <t>テスト種別</t>
   </si>
   <si>
     <t>テスト項目</t>
@@ -48,23 +51,383 @@
     <t>操作手順</t>
   </si>
   <si>
-    <t>期待結果</t>
-  </si>
-  <si>
-    <t>合否</t>
+    <t>確認内容</t>
+  </si>
+  <si>
+    <t>期待される挙動</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>正常系</t>
+  </si>
+  <si>
+    <t>収支追加</t>
+  </si>
+  <si>
+    <t>支出レコードを追加できる</t>
+  </si>
+  <si>
+    <t>FAB(＋)をクリック→支出・食費・1000・2026-04-01 入力→追加</t>
+  </si>
+  <si>
+    <t>一覧に追加したレコードが表示される</t>
+  </si>
+  <si>
+    <t>食費 1000円のカードが一覧に表示される</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>収入レコードを追加できる</t>
+  </si>
+  <si>
+    <t>FAB(＋)→収入・給与・300000・2026-04-01→追加</t>
+  </si>
+  <si>
+    <t>一覧に収入レコードが追加される</t>
+  </si>
+  <si>
+    <t>給与 +¥300,000 が緑色で表示される</t>
+  </si>
+  <si>
+    <t>メモ付きで追加できる</t>
+  </si>
+  <si>
+    <t>FAB(＋)→支出・娯楽・5000・メモ「映画」→追加</t>
+  </si>
+  <si>
+    <t>メモが一覧に表示される</t>
+  </si>
+  <si>
+    <t>カード内に「映画」のメモが表示される</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>異常系</t>
+  </si>
+  <si>
+    <t>金額 0 は追加できない</t>
+  </si>
+  <si>
+    <t>FAB(＋)→支出・食費・0→追加</t>
+  </si>
+  <si>
+    <t>エラーメッセージが表示される</t>
+  </si>
+  <si>
+    <t>「入力値を確認してください」が赤字で表示され追加されない</t>
+  </si>
+  <si>
+    <t>金額が小数は追加できない</t>
+  </si>
+  <si>
+    <t>FAB(＋)→支出・食費・100.5→追加</t>
+  </si>
+  <si>
+    <t>金額が空は追加できない</t>
+  </si>
+  <si>
+    <t>FAB(＋)→支出・食費・(空)→追加</t>
+  </si>
+  <si>
+    <t>日付は当日がデフォルト設定される</t>
+  </si>
+  <si>
+    <t>FAB(＋)をクリックして日付フィールドを確認</t>
+  </si>
+  <si>
+    <t>日付フィールドに当日の日付が設定されている</t>
+  </si>
+  <si>
+    <t>システム日付と同じ値が入力済みになっている</t>
+  </si>
+  <si>
+    <t>種別切替でカテゴリが変わる</t>
+  </si>
+  <si>
+    <t>FAB(＋)→収入を選択してカテゴリ選択肢を確認</t>
+  </si>
+  <si>
+    <t>カテゴリに収入カテゴリが表示される</t>
+  </si>
+  <si>
+    <t>給与・ボーナス・副収入・投資・その他収入が表示される</t>
+  </si>
+  <si>
+    <t>収支編集</t>
+  </si>
+  <si>
+    <t>レコードを編集できる</t>
+  </si>
+  <si>
+    <t>一覧のレコードをクリック→金額を 2000 に変更→更新</t>
+  </si>
+  <si>
+    <t>一覧の金額が更新される</t>
+  </si>
+  <si>
+    <t>対象カードの金額が¥2,000 に変更されている</t>
+  </si>
+  <si>
+    <t>カテゴリを編集できる</t>
+  </si>
+  <si>
+    <t>一覧のレコードをクリック→カテゴリを「交通費」に変更→更新</t>
+  </si>
+  <si>
+    <t>一覧のカテゴリが更新される</t>
+  </si>
+  <si>
+    <t>対象カードのカテゴリが「交通費」に変更されている</t>
+  </si>
+  <si>
+    <t>編集モーダルに既存値が設定される</t>
+  </si>
+  <si>
+    <t>既存レコードをクリックしてフォームを確認</t>
+  </si>
+  <si>
+    <t>各フィールドに保存済みの値が入っている</t>
+  </si>
+  <si>
+    <t>日付・種別・カテゴリ・金額・メモが元の値で表示される</t>
+  </si>
+  <si>
+    <t>編集モードに削除ボタンが表示される</t>
+  </si>
+  <si>
+    <t>既存レコードをクリックしてモーダルを確認</t>
+  </si>
+  <si>
+    <t>「削除」ボタンが表示されている</t>
+  </si>
+  <si>
+    <t>追加モードでは非表示、編集モードでは表示される</t>
+  </si>
+  <si>
+    <t>収支削除</t>
+  </si>
+  <si>
+    <t>レコードを削除できる</t>
+  </si>
+  <si>
+    <t>既存レコードをクリック→削除→確認ダイアログで OK</t>
+  </si>
+  <si>
+    <t>一覧から対象レコードが消える</t>
+  </si>
+  <si>
+    <t>削除したカードが一覧から除去され、サマリーも更新される</t>
+  </si>
+  <si>
+    <t>削除確認ダイアログでキャンセルは操作されない</t>
+  </si>
+  <si>
+    <t>削除→確認ダイアログでキャンセル</t>
+  </si>
+  <si>
+    <t>レコードが削除されない</t>
+  </si>
+  <si>
+    <t>一覧に元のレコードがそのまま残る</t>
+  </si>
+  <si>
+    <t>全レコード削除後は空メッセージが表示される</t>
+  </si>
+  <si>
+    <t>当月の全レコードを削除</t>
+  </si>
+  <si>
+    <t>「記録がありません」が表示される</t>
+  </si>
+  <si>
+    <t>空メッセージが表示される</t>
+  </si>
+  <si>
+    <t>月ナビゲーション</t>
+  </si>
+  <si>
+    <t>前月ボタンで前月に切り替わる</t>
+  </si>
+  <si>
+    <t>ヘッダーの ‹ ボタンをクリック</t>
+  </si>
+  <si>
+    <t>ヘッダーの月表示が前月になる</t>
+  </si>
+  <si>
+    <t>例：2026年4月 → 2026年3月 に変わる</t>
+  </si>
+  <si>
+    <t>翌月ボタンで翌月に切り替わる</t>
+  </si>
+  <si>
+    <t>ヘッダーの › ボタンをクリック</t>
+  </si>
+  <si>
+    <t>ヘッダーの月表示が翌月になる</t>
+  </si>
+  <si>
+    <t>例：2026年4月 → 2026年5月 に変わる</t>
+  </si>
+  <si>
+    <t>別月のレコードは表示されない</t>
+  </si>
+  <si>
+    <t>5月にレコードを追加後、ヘッダーで4月に戻る</t>
+  </si>
+  <si>
+    <t>4月の一覧に5月のレコードが表示されない</t>
+  </si>
+  <si>
+    <t>月ごとにデータがフィルタリングされている</t>
+  </si>
+  <si>
+    <t>年をまたぐ月切替ができる</t>
+  </si>
+  <si>
+    <t>1月表示で ‹ ボタンをクリック</t>
+  </si>
+  <si>
+    <t>前年12月に切り替わる</t>
+  </si>
+  <si>
+    <t>例：2026年1月 → 2025年12月 に変わる</t>
+  </si>
+  <si>
+    <t>サマリー計算</t>
+  </si>
+  <si>
+    <t>収入合計が正しく計算される</t>
+  </si>
+  <si>
+    <t>給与30万・副収入5万を追加してサマリーを確認</t>
+  </si>
+  <si>
+    <t>収入カードに¥350,000 が表示される</t>
+  </si>
+  <si>
+    <t>すべての収入レコードの合計が表示される</t>
+  </si>
+  <si>
+    <t>支出合計が正しく計算される</t>
+  </si>
+  <si>
+    <t>食費1万・交通費3千を追加してサマリーを確認</t>
+  </si>
+  <si>
+    <t>支出カードに¥13,000 が表示される</t>
+  </si>
+  <si>
+    <t>すべての支出レコードの合計が表示される</t>
+  </si>
+  <si>
+    <t>残高が正しく計算される</t>
+  </si>
+  <si>
+    <t>収入20万・支出5万を追加してサマリーを確認</t>
+  </si>
+  <si>
+    <t>残高カードに¥150,000 が表示される</t>
+  </si>
+  <si>
+    <t>収入 − 支出 が正しく表示される</t>
+  </si>
+  <si>
+    <t>残高がマイナスの場合も表示される</t>
+  </si>
+  <si>
+    <t>支出のみ追加してサマリーを確認</t>
+  </si>
+  <si>
+    <t>残高カードに負の金額が表示される</t>
+  </si>
+  <si>
+    <t>¥-10,000 のように負の値が正しく表示される</t>
+  </si>
+  <si>
+    <t>チャート表示</t>
+  </si>
+  <si>
+    <t>支出カテゴリのチャートが表示される</t>
+  </si>
+  <si>
+    <t>複数カテゴリの支出を追加してチャートを確認</t>
+  </si>
+  <si>
+    <t>ドーナツチャートが描画される</t>
+  </si>
+  <si>
+    <t>カテゴリ別のチャートと凡例が表示される</t>
+  </si>
+  <si>
+    <t>支出がない場合は空メッセージを表示</t>
+  </si>
+  <si>
+    <t>収入のみ追加してチャートを確認</t>
+  </si>
+  <si>
+    <t>「支出データがありません」が表示される</t>
+  </si>
+  <si>
+    <t>チャートは非表示になり、テキストが表示される</t>
+  </si>
+  <si>
+    <t>月切替でチャートが更新される</t>
+  </si>
+  <si>
+    <t>別月に切り替えてチャートを確認</t>
+  </si>
+  <si>
+    <t>切替後の月の支出で再描画される</t>
+  </si>
+  <si>
+    <t>前月のデータではなく当月のデータが反映される</t>
+  </si>
+  <si>
+    <t>CSV出力</t>
+  </si>
+  <si>
+    <t>当月レコードを CSV でダウンロードできる</t>
+  </si>
+  <si>
+    <t>レコードを追加後、「CSV出力」ボタンをクリック</t>
+  </si>
+  <si>
+    <t>CSV ファイルがダウンロードされる</t>
+  </si>
+  <si>
+    <t>moneybook_2026-04.csv がダウンロードされる</t>
+  </si>
+  <si>
+    <t>CSV のヘッダー行が正しい</t>
+  </si>
+  <si>
+    <t>ダウンロードした CSV をテキストエディタで確認</t>
+  </si>
+  <si>
+    <t>1行目がヘッダー行になっている</t>
+  </si>
+  <si>
+    <t>「日付,種別,カテゴリ,金額,メモ」の順で記載される</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -72,30 +435,16 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="游ゴシック"/>
       <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -112,12 +461,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -134,6 +492,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestSpec" displayName="TestSpec" ref="A1:H29" headerRowCount="1">
+  <autoFilter ref="A1:H29"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="No"/>
+    <tableColumn id="2" name="ステージ"/>
+    <tableColumn id="3" name="テスト種別"/>
+    <tableColumn id="4" name="テスト項目"/>
+    <tableColumn id="5" name="操作手順"/>
+    <tableColumn id="6" name="確認内容"/>
+    <tableColumn id="7" name="期待される挙動"/>
+    <tableColumn id="8" name="優先度"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,38 +807,778 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E153C9F8-1893-4D73-BB20-03ABAB9AEB15}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1" style="2"/>
+    <col min="2" max="2" width="12" customWidth="1" style="2"/>
+    <col min="3" max="3" width="18" customWidth="1" style="2"/>
+    <col min="4" max="4" width="36" customWidth="1" style="2"/>
+    <col min="5" max="5" width="46" customWidth="1" style="2"/>
+    <col min="6" max="6" width="36" customWidth="1" style="2"/>
+    <col min="7" max="7" width="46" customWidth="1" style="2"/>
+    <col min="8" max="8" width="10" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -73,12 +73,12 @@
     <t>正常系</t>
   </si>
   <si>
+    <t>収支追加</t>
+  </si>
+  <si>
     <t>K-01</t>
   </si>
   <si>
-    <t>収支追加</t>
-  </si>
-  <si>
     <t>FAB(+)で支出・食費・1000円・2026-04-01を入力して追加する</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>給与・ボーナス・副収入・投資・その他収入が表示される</t>
   </si>
   <si>
+    <t>収支編集</t>
+  </si>
+  <si>
     <t>K-09</t>
   </si>
   <si>
-    <t>収支編集</t>
-  </si>
-  <si>
     <t>既存レコードをクリックして金額を2000に変更し更新する</t>
   </si>
   <si>
@@ -190,12 +190,12 @@
     <t>「削除」ボタンが表示される（追加モードでは非表示）</t>
   </si>
   <si>
+    <t>収支削除</t>
+  </si>
+  <si>
     <t>K-13</t>
   </si>
   <si>
-    <t>収支削除</t>
-  </si>
-  <si>
     <t>既存レコードをクリックし削除→確認ダイアログでOKを押す</t>
   </si>
   <si>
@@ -220,12 +220,12 @@
     <t>「記録がありません」の空メッセージが表示される</t>
   </si>
   <si>
+    <t>月ナビゲーション</t>
+  </si>
+  <si>
     <t>K-16</t>
   </si>
   <si>
-    <t>月ナビゲーション</t>
-  </si>
-  <si>
     <t>ヘッダーの「‹」ボタンをクリックする</t>
   </si>
   <si>
@@ -259,12 +259,12 @@
     <t>前年12月に切り替わる（例: 2026年1月→2025年12月）</t>
   </si>
   <si>
+    <t>サマリー計算</t>
+  </si>
+  <si>
     <t>K-20</t>
   </si>
   <si>
-    <t>サマリー計算</t>
-  </si>
-  <si>
     <t>給与30万・副収入5万を追加してサマリーを確認する</t>
   </si>
   <si>
@@ -298,12 +298,12 @@
     <t>残高カードに負の金額（例: ¥-10,000）が正しく表示される</t>
   </si>
   <si>
+    <t>チャート表示</t>
+  </si>
+  <si>
     <t>K-24</t>
   </si>
   <si>
-    <t>チャート表示</t>
-  </si>
-  <si>
     <t>複数カテゴリの支出を追加してチャートを確認する</t>
   </si>
   <si>
@@ -328,10 +328,10 @@
     <t>切替後の月の支出データでチャートが再描画される</t>
   </si>
   <si>
+    <t>CSV出力</t>
+  </si>
+  <si>
     <t>K-27</t>
-  </si>
-  <si>
-    <t>CSV出力</t>
   </si>
   <si>
     <t>レコード追加後、「CSV出力」ボタンをクリックする</t>
@@ -566,13 +566,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>21</v>
@@ -601,13 +601,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>25</v>
@@ -636,13 +636,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>28</v>
@@ -671,13 +671,13 @@
         <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>32</v>
@@ -706,13 +706,13 @@
         <v>30</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>35</v>
@@ -741,13 +741,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>38</v>
@@ -776,13 +776,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>40</v>
@@ -811,13 +811,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>43</v>
@@ -846,13 +846,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>47</v>
@@ -881,13 +881,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>50</v>
@@ -916,13 +916,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>53</v>
@@ -951,13 +951,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>56</v>
@@ -986,13 +986,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>60</v>
@@ -1021,13 +1021,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>63</v>
@@ -1056,13 +1056,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>66</v>
@@ -1091,13 +1091,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>70</v>
@@ -1126,13 +1126,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>72</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>73</v>
@@ -1161,13 +1161,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>76</v>
@@ -1196,13 +1196,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>78</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>79</v>
@@ -1231,13 +1231,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>83</v>
@@ -1266,13 +1266,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>86</v>
@@ -1301,13 +1301,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>88</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>89</v>
@@ -1336,13 +1336,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>92</v>
@@ -1371,13 +1371,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>96</v>
@@ -1406,13 +1406,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>98</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>99</v>
@@ -1441,13 +1441,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>101</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>102</v>
@@ -1476,13 +1476,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>106</v>
@@ -1511,13 +1511,13 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>108</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>109</v>
@@ -1546,13 +1546,13 @@
         <v>30</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>111</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>112</v>

--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
   <si>
     <t>システム名</t>
   </si>
@@ -40,7 +40,10 @@
     <t>項番</t>
   </si>
   <si>
-    <t>故障状況</t>
+    <t>正常/異常</t>
+  </si>
+  <si>
+    <t>テスト種別</t>
   </si>
   <si>
     <t>ステージ</t>
@@ -52,7 +55,7 @@
     <t>カテゴリ</t>
   </si>
   <si>
-    <t>確認内容</t>
+    <t>確認内容・手順</t>
   </si>
   <si>
     <t>期待される挙動</t>
@@ -73,6 +76,9 @@
     <t>正常系</t>
   </si>
   <si>
+    <t>WB</t>
+  </si>
+  <si>
     <t>V</t>
   </si>
   <si>
@@ -404,6 +410,81 @@
   </si>
   <si>
     <t>formatYearMonth: 空文字を渡す</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>UI-BB01</t>
+  </si>
+  <si>
+    <t>画面操作</t>
+  </si>
+  <si>
+    <t>アプリを開き、日付欄を空白のまま「追加」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>「日付が不正です」エラーが表示され、レコードが追加されない</t>
+  </si>
+  <si>
+    <t>UI-BB02</t>
+  </si>
+  <si>
+    <t>金額欄に「0」を入力して「追加」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>「金額は1以上の整数を入力してください」エラーが表示される</t>
+  </si>
+  <si>
+    <t>UI-BB03</t>
+  </si>
+  <si>
+    <t>金額欄に「-100」を入力して「追加」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>UI-BB04</t>
+  </si>
+  <si>
+    <t>金額欄に「1.5」（小数）を入力して「追加」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>UI-BB05</t>
+  </si>
+  <si>
+    <t>日付・種別（収入）・カテゴリ・金額の全項目を有効な値で入力して「追加」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>一覧にレコードが追加表示され、合計金額が更新される</t>
+  </si>
+  <si>
+    <t>UI-BB06</t>
+  </si>
+  <si>
+    <t>一覧のレコードの「編集」ボタンをクリックし、金額を変更して「更新」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>一覧の該当レコードの金額が更新表示され、合計が再計算される</t>
+  </si>
+  <si>
+    <t>UI-BB07</t>
+  </si>
+  <si>
+    <t>一覧のレコードの「削除」ボタンをクリックし、確認ダイアログで「OK」を選択する</t>
+  </si>
+  <si>
+    <t>レコードが一覧から削除され（0件なら空状態メッセージ）合計が再計算される</t>
+  </si>
+  <si>
+    <t>UI-BB08</t>
+  </si>
+  <si>
+    <t>一覧のレコードの「削除」ボタンをクリックし、確認ダイアログで「キャンセル」を選択する</t>
+  </si>
+  <si>
+    <t>レコードは削除されずそのまま残る</t>
   </si>
   <si>
     <t>OK</t>
@@ -498,20 +579,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,1015 +655,1372 @@
       <c r="K7" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="L7" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4">
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10">
       <c r="A10" s="5">
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
     </row>
     <row r="11">
       <c r="A11" s="5">
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12">
       <c r="A12" s="5">
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="5">
         <v>6</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="5"/>
+        <v>38</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
     </row>
     <row r="14">
       <c r="A14" s="5">
         <v>7</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15">
       <c r="A15" s="4">
         <v>8</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="5">
         <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="5">
         <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
     </row>
     <row r="18">
       <c r="A18" s="5">
         <v>11</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="5"/>
+        <v>51</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
     </row>
     <row r="19">
       <c r="A19" s="5">
         <v>12</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
     </row>
     <row r="20">
       <c r="A20" s="4">
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="5">
         <v>14</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="G21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
     </row>
     <row r="22">
       <c r="A22" s="5">
         <v>15</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
     </row>
     <row r="23">
       <c r="A23" s="5">
         <v>16</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
     </row>
     <row r="24">
       <c r="A24" s="5">
         <v>17</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
     </row>
     <row r="25">
       <c r="A25" s="4">
         <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="5">
         <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H26" s="5"/>
+        <v>74</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
     </row>
     <row r="27">
       <c r="A27" s="5">
         <v>20</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H27" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
     </row>
     <row r="28">
       <c r="A28" s="4">
         <v>21</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="5">
         <v>22</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="5"/>
+        <v>85</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
     </row>
     <row r="30">
       <c r="A30" s="4">
         <v>23</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
     </row>
     <row r="31">
       <c r="A31" s="5">
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
     </row>
     <row r="32">
       <c r="A32" s="4">
         <v>25</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H32" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="5">
         <v>26</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H33" s="5"/>
+        <v>97</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
     </row>
     <row r="34">
       <c r="A34" s="4">
         <v>27</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H34" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
     </row>
     <row r="35">
       <c r="A35" s="4">
         <v>28</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H35" s="4"/>
+        <v>103</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
     </row>
     <row r="36">
       <c r="A36" s="4">
         <v>29</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H36" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
     </row>
     <row r="37">
       <c r="A37" s="5">
         <v>30</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H37" s="5"/>
+        <v>109</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
     </row>
     <row r="38">
       <c r="A38" s="5">
         <v>31</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H38" s="5"/>
+        <v>112</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
     </row>
     <row r="39">
       <c r="A39" s="5">
         <v>32</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="F39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
     </row>
     <row r="40">
       <c r="A40" s="4">
         <v>33</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H40" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
     </row>
     <row r="41">
       <c r="A41" s="4">
         <v>34</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H41" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
     </row>
     <row r="42">
       <c r="A42" s="5">
         <v>35</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H42" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>126</v>
+      </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
     </row>
     <row r="43">
       <c r="A43" s="4">
         <v>36</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="H43" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
     </row>
     <row r="44">
       <c r="A44" s="5">
         <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H44" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>126</v>
+      </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4">
+        <v>42</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4">
+        <v>43</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4">
+        <v>44</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="B8:B44" showErrorMessage="1">
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="B8:B52" showErrorMessage="1">
       <formula1>マスタ!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H8:H44" showErrorMessage="1">
+    <dataValidation type="list" sqref="C8:C52" showErrorMessage="1">
+      <formula1>マスタ!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I8:I52" showErrorMessage="1">
       <formula1>マスタ!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I8:I44" showErrorMessage="1">
+    <dataValidation type="list" sqref="J8:J52" showErrorMessage="1">
       <formula1>マスタ!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1591,7 +2030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,6 +2057,9 @@
       </c>
       <c r="H1" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1627,11 +2069,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1639,31 +2082,40 @@
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>130</v>
+        <v>157</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>131</v>
+        <v>158</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>システム名</t>
   </si>
@@ -79,7 +79,7 @@
     <t>WB</t>
   </si>
   <si>
-    <t>V</t>
+    <t>収支追加</t>
   </si>
   <si>
     <t>V-01</t>
@@ -181,9 +181,6 @@
     <t>validateRecord: amount が空文字</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>B-01</t>
   </si>
   <si>
@@ -211,9 +208,6 @@
     <t>validateBudget: limit = 1.5（小数）</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>S-01</t>
   </si>
   <si>
@@ -235,6 +229,9 @@
     <t>records に追加され、生成した ID を返す</t>
   </si>
   <si>
+    <t>収支編集</t>
+  </si>
+  <si>
     <t>S-03</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t>対象レコードが更新され storage に保存される</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>E-01</t>
   </si>
   <si>
@@ -286,6 +280,9 @@
     <t>records.map(renderRecordItem) で一覧を描画</t>
   </si>
   <si>
+    <t>チャート表示</t>
+  </si>
+  <si>
     <t>E-03</t>
   </si>
   <si>
@@ -349,6 +346,9 @@
     <t>form-error に「入力値を確認してください」を表示する</t>
   </si>
   <si>
+    <t>収支削除</t>
+  </si>
+  <si>
     <t>E-10</t>
   </si>
   <si>
@@ -373,7 +373,7 @@
     <t>deleteRecord() が呼ばれてモーダルを閉じ _refresh() が実行される</t>
   </si>
   <si>
-    <t>F</t>
+    <t>サマリー計算</t>
   </si>
   <si>
     <t>F-01</t>
@@ -413,9 +413,6 @@
   </si>
   <si>
     <t>BB</t>
-  </si>
-  <si>
-    <t>UI</t>
   </si>
   <si>
     <t>UI-BB01</t>
@@ -1030,16 +1027,16 @@
         <v>20</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>25</v>
@@ -1060,16 +1057,16 @@
         <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>39</v>
@@ -1090,16 +1087,16 @@
         <v>20</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>47</v>
@@ -1120,16 +1117,16 @@
         <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>47</v>
@@ -1150,19 +1147,19 @@
         <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -1180,19 +1177,19 @@
         <v>20</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="G25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1210,19 +1207,19 @@
         <v>20</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -1240,19 +1237,19 @@
         <v>20</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -1270,19 +1267,19 @@
         <v>20</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1300,19 +1297,19 @@
         <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
@@ -1330,19 +1327,19 @@
         <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="G30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1360,19 +1357,19 @@
         <v>20</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
@@ -1390,19 +1387,19 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1420,19 +1417,19 @@
         <v>20</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -1450,19 +1447,19 @@
         <v>20</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="H34" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -1480,19 +1477,19 @@
         <v>20</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -1510,19 +1507,19 @@
         <v>20</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G36" s="4" t="s">
+      <c r="H36" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -1540,19 +1537,19 @@
         <v>20</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -1570,13 +1567,13 @@
         <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>111</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>112</v>
@@ -1600,13 +1597,13 @@
         <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>114</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>115</v>
@@ -1630,13 +1627,13 @@
         <v>20</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>116</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>117</v>
@@ -1780,19 +1777,19 @@
         <v>132</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -1810,19 +1807,19 @@
         <v>132</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E46" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G46" s="5" t="s">
+      <c r="H46" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -1840,19 +1837,19 @@
         <v>132</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="H47" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
@@ -1870,19 +1867,19 @@
         <v>132</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="H48" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
@@ -1900,19 +1897,19 @@
         <v>132</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G49" s="4" t="s">
+      <c r="H49" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -1930,19 +1927,19 @@
         <v>132</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G50" s="4" t="s">
+      <c r="H50" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -1960,19 +1957,19 @@
         <v>132</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="E51" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G51" s="4" t="s">
+      <c r="H51" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -1990,19 +1987,19 @@
         <v>132</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="E52" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F52" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G52" s="5" t="s">
+      <c r="H52" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -2093,7 +2090,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>20</v>
@@ -2104,7 +2101,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>132</v>
@@ -2112,10 +2109,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>159</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -424,7 +424,7 @@
     <t>アプリを開き、日付欄を空白のまま「追加」ボタンをクリックする</t>
   </si>
   <si>
-    <t>「日付が不正です」エラーが表示され、レコードが追加されない</t>
+    <t>フォームエリアに「入力値を確認してください」エラーが表示され、レコードが追加されない</t>
   </si>
   <si>
     <t>UI-BB02</t>
@@ -433,7 +433,7 @@
     <t>金額欄に「0」を入力して「追加」ボタンをクリックする</t>
   </si>
   <si>
-    <t>「金額は1以上の整数を入力してください」エラーが表示される</t>
+    <t>フォームエリアに「入力値を確認してください」エラーが表示される</t>
   </si>
   <si>
     <t>UI-BB03</t>

--- a/docs/テスト仕様書/テスト仕様書.xlsx
+++ b/docs/テスト仕様書/テスト仕様書.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>システム名</t>
   </si>
@@ -430,7 +430,7 @@
     <t>UI-BB02</t>
   </si>
   <si>
-    <t>金額欄に「0」を入力して「追加」ボタンをクリックする</t>
+    <t>金額欄に不正な値（例: 0）を入力して「追加」ボタンをクリックする</t>
   </si>
   <si>
     <t>フォームエリアに「入力値を確認してください」エラーが表示される</t>
@@ -439,43 +439,31 @@
     <t>UI-BB03</t>
   </si>
   <si>
-    <t>金額欄に「-100」を入力して「追加」ボタンをクリックする</t>
+    <t>日付・種別（収入）・カテゴリ・金額の全項目を有効な値で入力して「追加」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>一覧にレコードが追加表示され、合計金額が更新される</t>
   </si>
   <si>
     <t>UI-BB04</t>
   </si>
   <si>
-    <t>金額欄に「1.5」（小数）を入力して「追加」ボタンをクリックする</t>
+    <t>一覧のレコードの「編集」ボタンをクリックし、金額を変更して「更新」ボタンをクリックする</t>
+  </si>
+  <si>
+    <t>一覧の該当レコードの金額が更新表示され、合計が再計算される</t>
   </si>
   <si>
     <t>UI-BB05</t>
   </si>
   <si>
-    <t>日付・種別（収入）・カテゴリ・金額の全項目を有効な値で入力して「追加」ボタンをクリックする</t>
-  </si>
-  <si>
-    <t>一覧にレコードが追加表示され、合計金額が更新される</t>
+    <t>一覧のレコードの「削除」ボタンをクリックし、確認ダイアログで「OK」を選択する</t>
+  </si>
+  <si>
+    <t>レコードが一覧から削除され（0件なら空状態メッセージ）合計が再計算される</t>
   </si>
   <si>
     <t>UI-BB06</t>
-  </si>
-  <si>
-    <t>一覧のレコードの「編集」ボタンをクリックし、金額を変更して「更新」ボタンをクリックする</t>
-  </si>
-  <si>
-    <t>一覧の該当レコードの金額が更新表示され、合計が再計算される</t>
-  </si>
-  <si>
-    <t>UI-BB07</t>
-  </si>
-  <si>
-    <t>一覧のレコードの「削除」ボタンをクリックし、確認ダイアログで「OK」を選択する</t>
-  </si>
-  <si>
-    <t>レコードが一覧から削除され（0件なら空状態メッセージ）合計が再計算される</t>
-  </si>
-  <si>
-    <t>UI-BB08</t>
   </si>
   <si>
     <t>一覧のレコードの「削除」ボタンをクリックし、確認ダイアログで「キャンセル」を選択する</t>
@@ -576,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1827,64 +1815,64 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>40</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="B47" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="5" t="s">
+      <c r="D47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="H47" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
+      <c r="H47" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
     </row>
     <row r="48">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <v>41</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C48" s="5" t="s">
+      <c r="B48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F48" s="5" t="s">
+      <c r="D48" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
+      <c r="G48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
     </row>
     <row r="49">
       <c r="A49" s="4">
@@ -1897,19 +1885,19 @@
         <v>132</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>134</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -1917,107 +1905,47 @@
       <c r="L49" s="4"/>
     </row>
     <row r="50">
-      <c r="A50" s="4">
+      <c r="A50" s="5">
         <v>43</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="B50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F50" s="4" t="s">
+      <c r="D50" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4">
-        <v>44</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E51" s="4" t="s">
+      <c r="G50" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G51" s="4" t="s">
+      <c r="H50" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="H51" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="B8:B52" showErrorMessage="1">
+    <dataValidation type="list" sqref="B8:B50" showErrorMessage="1">
       <formula1>マスタ!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C8:C52" showErrorMessage="1">
+    <dataValidation type="list" sqref="C8:C50" showErrorMessage="1">
       <formula1>マスタ!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I8:I52" showErrorMessage="1">
+    <dataValidation type="list" sqref="I8:I50" showErrorMessage="1">
       <formula1>マスタ!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J8:J52" showErrorMessage="1">
+    <dataValidation type="list" sqref="J8:J50" showErrorMessage="1">
       <formula1>マスタ!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -2090,7 +2018,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>20</v>
@@ -2101,7 +2029,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>132</v>
@@ -2109,10 +2037,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
